--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48842,6 +48842,14 @@
         <v>13065.0</v>
       </c>
     </row>
+    <row r="6105">
+      <c r="A6105" t="str">
+        <v>2026-07-18</v>
+      </c>
+      <c r="B6105">
+        <v>13135.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48850,6 +48850,14 @@
         <v>13135.0</v>
       </c>
     </row>
+    <row r="6106">
+      <c r="A6106" t="str">
+        <v>2026-07-19</v>
+      </c>
+      <c r="B6106">
+        <v>13135.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48858,6 +48858,14 @@
         <v>13135.0</v>
       </c>
     </row>
+    <row r="6107">
+      <c r="A6107" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="B6107">
+        <v>13150.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48866,6 +48866,14 @@
         <v>13150.0</v>
       </c>
     </row>
+    <row r="6108">
+      <c r="A6108" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="B6108">
+        <v>13220.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48874,6 +48874,14 @@
         <v>13220.0</v>
       </c>
     </row>
+    <row r="6109">
+      <c r="A6109" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="B6109">
+        <v>13430.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48882,6 +48882,22 @@
         <v>13430.0</v>
       </c>
     </row>
+    <row r="6110">
+      <c r="A6110" t="str">
+        <v>2026-07-23</v>
+      </c>
+      <c r="B6110">
+        <v>13400.0</v>
+      </c>
+    </row>
+    <row r="6111">
+      <c r="A6111" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="B6111">
+        <v>13230.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48898,6 +48898,14 @@
         <v>13230.0</v>
       </c>
     </row>
+    <row r="6112">
+      <c r="A6112" t="str">
+        <v>2026-07-25</v>
+      </c>
+      <c r="B6112">
+        <v>13285.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48906,6 +48906,14 @@
         <v>13285.0</v>
       </c>
     </row>
+    <row r="6113">
+      <c r="A6113" t="str">
+        <v>2026-07-26</v>
+      </c>
+      <c r="B6113">
+        <v>13285.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48914,6 +48914,14 @@
         <v>13285.0</v>
       </c>
     </row>
+    <row r="6114">
+      <c r="A6114" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="B6114">
+        <v>13370.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48922,6 +48922,14 @@
         <v>13370.0</v>
       </c>
     </row>
+    <row r="6115">
+      <c r="A6115" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="B6115">
+        <v>13215.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48930,6 +48930,14 @@
         <v>13215.0</v>
       </c>
     </row>
+    <row r="6116">
+      <c r="A6116" t="str">
+        <v>2026-07-29</v>
+      </c>
+      <c r="B6116">
+        <v>13155.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48938,6 +48938,14 @@
         <v>13155.0</v>
       </c>
     </row>
+    <row r="6117">
+      <c r="A6117" t="str">
+        <v>2026-07-30</v>
+      </c>
+      <c r="B6117">
+        <v>13230.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48946,6 +48946,14 @@
         <v>13230.0</v>
       </c>
     </row>
+    <row r="6118">
+      <c r="A6118" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="B6118">
+        <v>13220.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48954,6 +48954,14 @@
         <v>13220.0</v>
       </c>
     </row>
+    <row r="6119">
+      <c r="A6119" t="str">
+        <v>2026-08-02</v>
+      </c>
+      <c r="B6119">
+        <v>13220.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48962,6 +48962,22 @@
         <v>13220.0</v>
       </c>
     </row>
+    <row r="6120">
+      <c r="A6120" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="B6120">
+        <v>13220.0</v>
+      </c>
+    </row>
+    <row r="6121">
+      <c r="A6121" t="str">
+        <v>2026-08-04</v>
+      </c>
+      <c r="B6121">
+        <v>13200.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48978,6 +48978,14 @@
         <v>13200.0</v>
       </c>
     </row>
+    <row r="6122">
+      <c r="A6122" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="B6122">
+        <v>13360.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -48983,7 +48983,31 @@
         <v>2026-08-05</v>
       </c>
       <c r="B6122">
-        <v>13360.0</v>
+        <v>13460.0</v>
+      </c>
+    </row>
+    <row r="6123">
+      <c r="A6123" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="B6123">
+        <v>13725.0</v>
+      </c>
+    </row>
+    <row r="6124">
+      <c r="A6124" t="str">
+        <v>2026-08-07</v>
+      </c>
+      <c r="B6124">
+        <v>13865.0</v>
+      </c>
+    </row>
+    <row r="6125">
+      <c r="A6125" t="str">
+        <v>2026-08-08</v>
+      </c>
+      <c r="B6125">
+        <v>13965.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49010,6 +49010,14 @@
         <v>13965.0</v>
       </c>
     </row>
+    <row r="6126">
+      <c r="A6126" t="str">
+        <v>2026-08-09</v>
+      </c>
+      <c r="B6126">
+        <v>13965.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49018,6 +49018,14 @@
         <v>13965.0</v>
       </c>
     </row>
+    <row r="6127">
+      <c r="A6127" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="B6127">
+        <v>13930.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49026,6 +49026,14 @@
         <v>13930.0</v>
       </c>
     </row>
+    <row r="6128">
+      <c r="A6128" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="B6128">
+        <v>14220.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49031,7 +49031,15 @@
         <v>2026-08-11</v>
       </c>
       <c r="B6128">
-        <v>14220.0</v>
+        <v>14100.0</v>
+      </c>
+    </row>
+    <row r="6129">
+      <c r="A6129" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="B6129">
+        <v>14195.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49042,6 +49042,22 @@
         <v>14195.0</v>
       </c>
     </row>
+    <row r="6130">
+      <c r="A6130" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="B6130">
+        <v>14080.0</v>
+      </c>
+    </row>
+    <row r="6131">
+      <c r="A6131" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="B6131">
+        <v>14015.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49055,7 +49055,23 @@
         <v>2026-08-14</v>
       </c>
       <c r="B6131">
-        <v>14015.0</v>
+        <v>14155.0</v>
+      </c>
+    </row>
+    <row r="6132">
+      <c r="A6132" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="B6132">
+        <v>14220.0</v>
+      </c>
+    </row>
+    <row r="6133">
+      <c r="A6133" t="str">
+        <v>2026-08-16</v>
+      </c>
+      <c r="B6133">
+        <v>14220.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49074,6 +49074,14 @@
         <v>14220.0</v>
       </c>
     </row>
+    <row r="6134">
+      <c r="A6134" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="B6134">
+        <v>14270.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49082,6 +49082,14 @@
         <v>14270.0</v>
       </c>
     </row>
+    <row r="6135">
+      <c r="A6135" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="B6135">
+        <v>14290.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49090,6 +49090,14 @@
         <v>14290.0</v>
       </c>
     </row>
+    <row r="6136">
+      <c r="A6136" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="B6136">
+        <v>14205.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49098,6 +49098,14 @@
         <v>14205.0</v>
       </c>
     </row>
+    <row r="6137">
+      <c r="A6137" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B6137">
+        <v>14600.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49106,6 +49106,14 @@
         <v>14600.0</v>
       </c>
     </row>
+    <row r="6138">
+      <c r="A6138" t="str">
+        <v>2026-08-21</v>
+      </c>
+      <c r="B6138">
+        <v>14710.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49111,7 +49111,15 @@
         <v>2026-08-21</v>
       </c>
       <c r="B6138">
-        <v>14710.0</v>
+        <v>14810.0</v>
+      </c>
+    </row>
+    <row r="6139">
+      <c r="A6139" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="B6139">
+        <v>14950.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49122,6 +49122,14 @@
         <v>14950.0</v>
       </c>
     </row>
+    <row r="6140">
+      <c r="A6140" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="B6140">
+        <v>14950.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49130,6 +49130,14 @@
         <v>14950.0</v>
       </c>
     </row>
+    <row r="6141">
+      <c r="A6141" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="B6141">
+        <v>15030.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49138,6 +49138,14 @@
         <v>15030.0</v>
       </c>
     </row>
+    <row r="6142">
+      <c r="A6142" t="str">
+        <v>2026-08-25</v>
+      </c>
+      <c r="B6142">
+        <v>15010.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49146,6 +49146,14 @@
         <v>15010.0</v>
       </c>
     </row>
+    <row r="6143">
+      <c r="A6143" t="str">
+        <v>2026-08-26</v>
+      </c>
+      <c r="B6143">
+        <v>15010.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49154,6 +49154,14 @@
         <v>15010.0</v>
       </c>
     </row>
+    <row r="6144">
+      <c r="A6144" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="B6144">
+        <v>14940.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49159,7 +49159,15 @@
         <v>2026-08-27</v>
       </c>
       <c r="B6144">
-        <v>14940.0</v>
+        <v>14725.0</v>
+      </c>
+    </row>
+    <row r="6145">
+      <c r="A6145" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="B6145">
+        <v>14650.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49167,7 +49167,15 @@
         <v>2026-08-28</v>
       </c>
       <c r="B6145">
-        <v>14650.0</v>
+        <v>14770.0</v>
+      </c>
+    </row>
+    <row r="6146">
+      <c r="A6146" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="B6146">
+        <v>14505.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49178,6 +49178,14 @@
         <v>14505.0</v>
       </c>
     </row>
+    <row r="6147">
+      <c r="A6147" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="B6147">
+        <v>14505.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49186,6 +49186,14 @@
         <v>14505.0</v>
       </c>
     </row>
+    <row r="6148">
+      <c r="A6148" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="B6148">
+        <v>14370.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49194,6 +49194,14 @@
         <v>14370.0</v>
       </c>
     </row>
+    <row r="6149">
+      <c r="A6149" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="B6149">
+        <v>14385.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49199,7 +49199,15 @@
         <v>2026-09-01</v>
       </c>
       <c r="B6149">
-        <v>14385.0</v>
+        <v>14215.0</v>
+      </c>
+    </row>
+    <row r="6150">
+      <c r="A6150" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="B6150">
+        <v>13935.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49210,6 +49210,14 @@
         <v>13935.0</v>
       </c>
     </row>
+    <row r="6151">
+      <c r="A6151" t="str">
+        <v>2026-09-03</v>
+      </c>
+      <c r="B6151">
+        <v>14240.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49218,6 +49218,14 @@
         <v>14240.0</v>
       </c>
     </row>
+    <row r="6152">
+      <c r="A6152" t="str">
+        <v>2026-09-04</v>
+      </c>
+      <c r="B6152">
+        <v>14360.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49226,6 +49226,14 @@
         <v>14360.0</v>
       </c>
     </row>
+    <row r="6153">
+      <c r="A6153" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="B6153">
+        <v>14190.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>